--- a/mlef_pipeline/results/DCR/SQUAMOUS/RWD/results.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/RWD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.58 ± 0.06</t>
+          <t>0.41 ± 0.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72 ± 0.14</t>
+          <t>0.70 ± 0.36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.48 ± 0.05</t>
+          <t>0.39 ± 0.36</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.68 ± 0.13</t>
+          <t>0.59 ± 0.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.77 ± 0.18</t>
+          <t>0.62 ± 0.22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F4" t="n">
